--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-location.xlsx
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>.Role[classCode=SDLC]</t>
@@ -285,10 +285,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -301,10 +301,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -324,7 +324,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -340,10 +340,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -352,7 +352,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -372,10 +372,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -398,13 +398,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -427,7 +427,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -437,7 +437,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Location.modifierExtension</t>
@@ -446,7 +446,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -489,7 +489,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「場所がまだ使用されているかどうかを示します。」(Basho ga mada shiyou sarete iru ka dou ka wo shimeshimasu.)</t>
+    <t>「場所がまだ使用されているかどうかを示します。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
@@ -517,7 +517,7 @@
     <t>コードは、SNOMED CTなどの非常に形式的な定義まで、列挙またはコードリストで非常にカジュアルに定義できる。詳細については、HL7 v3コア原則を参照すること。</t>
   </si>
   <si>
-    <t>「通常ベッド/部屋が位置する場所の稼働状況」</t>
+    <t>通常ベッド/部屋が位置する場所の稼働状況</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v2-0116</t>
@@ -588,7 +588,7 @@
     <t>スケジュールや順番に場所リソースを使用する場合、特定の場所ではなく場所のクラスを参照できる必要がある。</t>
   </si>
   <si>
-    <t>「リソースインスタンスが特定の場所を表すのか、場所のクラスを表すのかを示します。」</t>
+    <t>リソースインスタンスが特定の場所を表すのか、場所のクラスを表すのかを示します。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/location-mode|4.0.1</t>
@@ -619,7 +619,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>「場所で行われる機能のタイプを示します。」(Basho de okonawareru kinou no taipu wo shimesu.)</t>
+    <t>「場所で行われる機能のタイプを示します。」</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
@@ -727,7 +727,7 @@
     <t>Location.position.extension</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -740,11 +740,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -1257,7 +1257,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="86.25390625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="43.953125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
